--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bt.stajyer\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62BD9798-7335-4809-B25A-41E5EAFBCCAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64AA2AC0-80DF-4C68-ADA1-344B1FCE8F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B05765D8-1BFC-41D6-B916-63AAD90E4244}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="96">
   <si>
     <t>question</t>
   </si>
@@ -56,227 +56,294 @@
     <t>correct_index</t>
   </si>
   <si>
-    <t>Esra kim sayesinde kariyer planını çizebildi?</t>
-  </si>
-  <si>
-    <t>Berkant</t>
-  </si>
-  <si>
-    <t>Berkant Aynagöz</t>
-  </si>
-  <si>
-    <t>Berkant Abisi</t>
-  </si>
-  <si>
-    <t>Berkant Bey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hangisi Uşak yöresine ait önemli bir yemektir? </t>
-  </si>
-  <si>
-    <t>Uşak Taktuk Helvası</t>
-  </si>
-  <si>
-    <t>Uşak Tarhanası</t>
-  </si>
-  <si>
-    <t>Uşak Sırık Kebabı</t>
-  </si>
-  <si>
-    <t>Uşak Hamursuz Tatlısı</t>
-  </si>
-  <si>
-    <t>Ofiste en çok hangi burç vardır?</t>
-  </si>
-  <si>
-    <t>Terazi</t>
-  </si>
-  <si>
-    <t>İkizler</t>
-  </si>
-  <si>
-    <t>Akrep</t>
-  </si>
-  <si>
-    <t>Kova</t>
-  </si>
-  <si>
-    <t>Yeşil ile mavi kombinini kim yapar ? </t>
-  </si>
-  <si>
-    <t>Esra</t>
-  </si>
-  <si>
-    <t>Murat</t>
-  </si>
-  <si>
-    <t>Rümeysa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murat Bey'in çocuğunun adı nedir? </t>
-  </si>
-  <si>
-    <t>Ali uras</t>
-  </si>
-  <si>
-    <t>Ömer uraz</t>
-  </si>
-  <si>
-    <t>Ali uraz</t>
-  </si>
-  <si>
-    <t>Asaf uraz</t>
-  </si>
-  <si>
-    <t>R*meysa'nın  tam adı nasıl yazılıyor?</t>
-  </si>
-  <si>
-    <t>Rümeysa Ağırca</t>
-  </si>
-  <si>
-    <t>Rumeysa Ağırca</t>
-  </si>
-  <si>
-    <t>Rumeysa Agırca</t>
-  </si>
-  <si>
-    <t>Rümeysa Ağarça</t>
-  </si>
-  <si>
-    <t>Abap'ın gereksiz olduğunu kim düşünüyor ?</t>
-  </si>
-  <si>
-    <t>Bilge</t>
-  </si>
-  <si>
-    <t>Rumeysa</t>
-  </si>
-  <si>
-    <t>Murat'ın baş düşmanı kimdir?</t>
-  </si>
-  <si>
-    <t>Özhan Bey</t>
-  </si>
-  <si>
-    <t>Murat Yıldız</t>
-  </si>
-  <si>
-    <t>Said Yaprak</t>
-  </si>
-  <si>
-    <t>Esra'nın yönetici olarak benimsediği kişilerin şirket atılmasına ne sebep oluyordur?</t>
-  </si>
-  <si>
-    <t>Esra'nın gözü</t>
-  </si>
-  <si>
-    <t>Esra'nın Laneti</t>
-  </si>
-  <si>
-    <t>Esra'nın Pijaması</t>
-  </si>
-  <si>
-    <t>Esra'nın Kuyu kazması</t>
-  </si>
-  <si>
-    <t>En çalışkan stajyer kimdir?</t>
-  </si>
-  <si>
-    <t>Bilge Büşra Arık</t>
-  </si>
-  <si>
-    <t>Ofisteki Asitli turşu suyunu kim içecek?</t>
-  </si>
-  <si>
-    <t>Murat Bey</t>
-  </si>
-  <si>
-    <t>Esranın kaç kardeşi vardır?</t>
-  </si>
-  <si>
-    <t>Kimin Cv'sinde Valilik stajı vardır ? </t>
-  </si>
-  <si>
-    <t>Kim balıktan daha değersiz ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rumeysa </t>
-  </si>
-  <si>
-    <t>Ekipte 'E' harfini 'EEĞ' olarak söyleyen kim değildir?</t>
-  </si>
-  <si>
-    <t>EEĞSRA</t>
-  </si>
-  <si>
-    <t>ABAPÇI</t>
-  </si>
-  <si>
-    <t>Uzman Yardımcısı</t>
-  </si>
-  <si>
-    <t>Bilgi Teknolojileri Stajyeri</t>
-  </si>
-  <si>
-    <t>Berkant'ın en sevdiği eşyası nedir?</t>
-  </si>
-  <si>
-    <t>Askeri kamuflaj hırka</t>
-  </si>
-  <si>
-    <t>Küpe olmayan ama küpe gibi duran kulaklık</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yeni aldığı yeşil keten eşofmanımsı pantolon </t>
-  </si>
-  <si>
     <t>Hepsi</t>
   </si>
   <si>
-    <t>SAP ABAP Uzman Yardımcısı Nerelidir? </t>
-  </si>
-  <si>
-    <t>San Francisco</t>
-  </si>
-  <si>
-    <t>Santiago</t>
-  </si>
-  <si>
-    <t>Sinop</t>
-  </si>
-  <si>
-    <t>Saraybosna</t>
-  </si>
-  <si>
-    <t>Bir somon balığı uğruna ekip arkadaşını yalnız bırakmayan koca yürekli adam gibi adam kişiler kimdir? </t>
-  </si>
-  <si>
-    <t>Esra ve Ezgi</t>
-  </si>
-  <si>
-    <t>Ezgi ve Şevva</t>
-  </si>
-  <si>
-    <t>Şevval ve Esr</t>
-  </si>
-  <si>
-    <t>Berkant ve Murat Bey </t>
-  </si>
-  <si>
-    <t>Dogru</t>
-  </si>
-  <si>
-    <t>Cevabı</t>
-  </si>
-  <si>
-    <t>Biliyorsun</t>
+    <t>Hangisi bir BI toolu değildir?</t>
+  </si>
+  <si>
+    <t>SAP BI</t>
+  </si>
+  <si>
+    <t>Tableau</t>
+  </si>
+  <si>
+    <t>Qlick</t>
+  </si>
+  <si>
+    <t>Matlab</t>
+  </si>
+  <si>
+    <t>Dumbledore Hogwart ta her sınıfın yıllık malzeme harcamalarını takip etmek istiyor. SAP’de hangi tanım kullanılır?</t>
+  </si>
+  <si>
+    <t>House Bank</t>
+  </si>
+  <si>
+    <t>Cost Center</t>
+  </si>
+  <si>
+    <t>Internal Order</t>
+  </si>
+  <si>
+    <t>İstanbul ofis ile Gebze ofis arası kaç km?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BTIS’nin açılımı nedir? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilgi Teknolojileri İyileştirme Stratejileri </t>
+  </si>
+  <si>
+    <t>Bütün Ticket'lar İçin Sorumlu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilgi Teknolojileri İş Çözümleri </t>
+  </si>
+  <si>
+    <t>Bilgi Transferi ve İnteraktif Sistemler</t>
+  </si>
+  <si>
+    <t>SAP MII'nin bir süper gücü olsaydı ne olurdu?</t>
+  </si>
+  <si>
+    <t>Zamanda yolculuk</t>
+  </si>
+  <si>
+    <t>Fabrikada görünmezlik</t>
+  </si>
+  <si>
+    <t>Gerçek zamanlı veriyle tüm üretimi şeffaf hale getirme</t>
+  </si>
+  <si>
+    <t>Çalışanların yerine rapor yazma</t>
+  </si>
+  <si>
+    <t>SuccessFactors “Learning Management System (LMS)” modülü ne işe yarar?</t>
+  </si>
+  <si>
+    <t>E-posta yönetimi</t>
+  </si>
+  <si>
+    <t>Uzaktan eğitim ve çalışan gelişimi süreçlerini yönetmek</t>
+  </si>
+  <si>
+    <t>Stok takibi yapmak</t>
+  </si>
+  <si>
+    <t>Vardiya planı oluşturmak</t>
+  </si>
+  <si>
+    <t>Toplantıda herkes farklı şeyler söylüyorsa, iş analisti ne yapmalıdır?</t>
+  </si>
+  <si>
+    <t>Tartışmayı bitirip kahve molası vermek</t>
+  </si>
+  <si>
+    <t>Tüm görüşleri not alıp ortak noktayı bulmaya çalışmak</t>
+  </si>
+  <si>
+    <t>En yüksek sesli konuşanın dediğini kabul etmek</t>
+  </si>
+  <si>
+    <t>Toplantıyı sessizce terk etmek</t>
+  </si>
+  <si>
+    <t>Teklif oluştururken müşteri alanı boş bırakılırsa ne olur?</t>
+  </si>
+  <si>
+    <t>Sistem uyarı verir ve teklif kaydedilemez</t>
+  </si>
+  <si>
+    <t>Müşteri kendi kendine seçilir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sipariş havada kaybolur </t>
+  </si>
+  <si>
+    <t>SAP sistemden atar</t>
+  </si>
+  <si>
+    <t>BREAK-POINT ile DEBUG MODE arasındaki ilişki nedir?</t>
+  </si>
+  <si>
+    <t>BREAK-POINT debug modunu başlatır</t>
+  </si>
+  <si>
+    <t>Debug modu BREAK-POINT’i bulur</t>
+  </si>
+  <si>
+    <t>İkisi de geliştiricinin “yakala-kaç” oyunu gibidir</t>
+  </si>
+  <si>
+    <t>İş zekası modülü ile uğraşan birinin ne yapması beklenmez?</t>
+  </si>
+  <si>
+    <t>Raporlarına hatalı dendiğinde doğru olduğunu ispatlamaya çalışması</t>
+  </si>
+  <si>
+    <t>Süreci başından alsın sonuna kadar götürmesi</t>
+  </si>
+  <si>
+    <t>İnsanların arkasında oturup, "Excel böyle mi kullanılır? Şu formülü yaz." Diye maydanoz olması</t>
+  </si>
+  <si>
+    <t>İstenen raporları yapması</t>
+  </si>
+  <si>
+    <t>CO modülünün temel amacı nedir?</t>
+  </si>
+  <si>
+    <t>Ürün maliyetlerini ve iç raporlamayı yönetmek</t>
+  </si>
+  <si>
+    <t>Satış fiyatlarını belirlemek</t>
+  </si>
+  <si>
+    <t>Banka hesaplarını yönetmek</t>
+  </si>
+  <si>
+    <t>JIRA'da Bilgi teknolojilerine ait kaç adet proje bulunmaktadır?</t>
+  </si>
+  <si>
+    <t>SAP’de en çok korkulan ekran hangisidir?</t>
+  </si>
+  <si>
+    <t>SM37 – İş Listesi</t>
+  </si>
+  <si>
+    <t>ST22 – Dump Raporu</t>
+  </si>
+  <si>
+    <t>SU01 – Kullanıcı Oluşturma</t>
+  </si>
+  <si>
+    <t>SE80 – Object Navigator</t>
+  </si>
+  <si>
+    <t>SAP MII hangi iki sistem arasında köprü görevi görür?</t>
+  </si>
+  <si>
+    <t>ERP ve CRM</t>
+  </si>
+  <si>
+    <t>MES ve ERP</t>
+  </si>
+  <si>
+    <t>SCM ve SRM</t>
+  </si>
+  <si>
+    <t>HCM ve BI</t>
+  </si>
+  <si>
+    <t>SAP sistemine yanlış veri girerseniz ne olur?</t>
+  </si>
+  <si>
+    <t>Sistem kahve molası verir</t>
+  </si>
+  <si>
+    <t>Veri reddedilir veya hata alırsınız</t>
+  </si>
+  <si>
+    <t>Patron size alkış tutar</t>
+  </si>
+  <si>
+    <t>Bilgisayar patlar</t>
+  </si>
+  <si>
+    <t>Büyük işletmelerde kullanılan uygulamaların verileri yerel ya da cloud da nerede tutulur?</t>
+  </si>
+  <si>
+    <t>Dolaplarda</t>
+  </si>
+  <si>
+    <t>Dosyalarda</t>
+  </si>
+  <si>
+    <t>Buzdolabında</t>
+  </si>
+  <si>
+    <t>Veritabanında</t>
+  </si>
+  <si>
+    <t>Rpa ne demek ?</t>
+  </si>
+  <si>
+    <t>Robotic Programing Automation</t>
+  </si>
+  <si>
+    <t>Robotic Programing Authentication</t>
+  </si>
+  <si>
+    <t>Robotic Process Automation</t>
+  </si>
+  <si>
+    <t>Robotic Process Authentication</t>
+  </si>
+  <si>
+    <t>SAP’nin ERP açılımı aşağıdakilerden hangisi değildir?</t>
+  </si>
+  <si>
+    <t>Enterprise Resource Planning</t>
+  </si>
+  <si>
+    <t>Kurumsal Kaynak Planlama</t>
+  </si>
+  <si>
+    <t>Resource &amp; Enterprise Planning</t>
+  </si>
+  <si>
+    <t>En Rahat Patron</t>
+  </si>
+  <si>
+    <t>Kod hatalı çalıştığında</t>
+  </si>
+  <si>
+    <t>Koşul sağlandığında veya işlem başarılı olduğunda</t>
+  </si>
+  <si>
+    <t>Sistem saatini gösterdiğinde</t>
+  </si>
+  <si>
+    <t>Bellek boş olduğunda</t>
+  </si>
+  <si>
+    <t>SAP MM modülünde aşağıdakilerden hangisi bulunmaz?</t>
+  </si>
+  <si>
+    <t>Malzeme Yönetimi</t>
+  </si>
+  <si>
+    <t>Satınalma</t>
+  </si>
+  <si>
+    <t>Depo Yönetimi</t>
+  </si>
+  <si>
+    <t>Moda ve Makyaj Yönetimi</t>
+  </si>
+  <si>
+    <r>
+      <t>SY-SUBRC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="162"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> değeri ne zaman 0 olur?</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,6 +367,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="162"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -321,10 +402,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -659,16 +741,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F608FC60-8EF4-4635-B0AF-614F7986C937}">
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="57.08984375" customWidth="1"/>
-    <col min="2" max="2" width="17.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="19.36328125" customWidth="1"/>
+    <col min="3" max="3" width="16.6328125" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="21.7265625" customWidth="1"/>
     <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -688,152 +772,152 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4">
+        <v>30</v>
+      </c>
+      <c r="C4">
+        <v>32</v>
+      </c>
+      <c r="D4">
+        <v>34</v>
+      </c>
+      <c r="E4">
+        <v>36</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="F4">
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="E5" t="s">
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="D6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" t="s">
+      <c r="E6" t="s">
         <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>29</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E7" t="s">
         <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>34</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
         <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" t="s">
-        <v>37</v>
       </c>
       <c r="E8" t="s">
         <v>36</v>
       </c>
       <c r="F8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
         <v>38</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
       </c>
       <c r="C9" t="s">
         <v>39</v>
@@ -845,206 +929,246 @@
         <v>41</v>
       </c>
       <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
         <v>47</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>46</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="F13">
         <v>3</v>
       </c>
-      <c r="E13">
-        <v>4</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17">
+    <row r="19" spans="1:6">
+      <c r="A19" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" t="s">
+        <v>94</v>
+      </c>
+      <c r="F20">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F19">
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21">
         <v>3</v>
       </c>
     </row>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bt.stajyer\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64AA2AC0-80DF-4C68-ADA1-344B1FCE8F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B1A03F-7C70-4E05-AE2F-02E913D76ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B05765D8-1BFC-41D6-B916-63AAD90E4244}"/>
   </bookViews>
@@ -179,18 +179,6 @@
     <t>İş zekası modülü ile uğraşan birinin ne yapması beklenmez?</t>
   </si>
   <si>
-    <t>Raporlarına hatalı dendiğinde doğru olduğunu ispatlamaya çalışması</t>
-  </si>
-  <si>
-    <t>Süreci başından alsın sonuna kadar götürmesi</t>
-  </si>
-  <si>
-    <t>İnsanların arkasında oturup, "Excel böyle mi kullanılır? Şu formülü yaz." Diye maydanoz olması</t>
-  </si>
-  <si>
-    <t>İstenen raporları yapması</t>
-  </si>
-  <si>
     <t>CO modülünün temel amacı nedir?</t>
   </si>
   <si>
@@ -338,12 +326,24 @@
       <t xml:space="preserve"> değeri ne zaman 0 olur?</t>
     </r>
   </si>
+  <si>
+    <t>Raporlarına hatalı dendiğinde doğru olduğunu ispatlamaya çalışmamalı</t>
+  </si>
+  <si>
+    <t>İnsanların arkasında oturup, "Excel böyle mi kullanılır? Şu formülü yaz." Diye maydanoz olmalı</t>
+  </si>
+  <si>
+    <t>Öyle istenen raporları yapmalı</t>
+  </si>
+  <si>
+    <t>Süreci başından alıp sonuna kadar götürmeli</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -365,14 +365,6 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -406,7 +398,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -957,16 +949,16 @@
         <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -974,16 +966,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -994,7 +986,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -1014,19 +1006,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" t="s">
         <v>56</v>
-      </c>
-      <c r="B14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>60</v>
       </c>
       <c r="F14">
         <v>2</v>
@@ -1034,19 +1026,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" t="s">
         <v>61</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" t="s">
-        <v>65</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1054,19 +1046,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
         <v>66</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" t="s">
-        <v>70</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1074,19 +1066,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
         <v>76</v>
-      </c>
-      <c r="B17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" t="s">
-        <v>80</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -1094,19 +1086,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
         <v>71</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" t="s">
-        <v>75</v>
       </c>
       <c r="F18">
         <v>3</v>
@@ -1114,19 +1106,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1134,19 +1126,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" t="s">
         <v>90</v>
-      </c>
-      <c r="B20" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" t="s">
-        <v>94</v>
       </c>
       <c r="F20">
         <v>3</v>
@@ -1154,19 +1146,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" t="s">
         <v>81</v>
-      </c>
-      <c r="B21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" t="s">
-        <v>85</v>
       </c>
       <c r="F21">
         <v>3</v>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bt.stajyer\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9EAD7A1-4C9D-4678-9255-2B1F0BD02897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E27070-2BBA-408E-9F38-69CE9BE42433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0D28B3CB-615D-4409-A43F-9F5C3AB403DB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B05765D8-1BFC-41D6-B916-63AAD90E4244}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="96">
   <si>
     <t>question</t>
   </si>
@@ -44,170 +44,306 @@
     <t>option1</t>
   </si>
   <si>
+    <t>option4</t>
+  </si>
+  <si>
+    <t>option3</t>
+  </si>
+  <si>
     <t>option2</t>
   </si>
   <si>
-    <t>option3</t>
-  </si>
-  <si>
-    <t>option4</t>
-  </si>
-  <si>
     <t>correct_index</t>
   </si>
   <si>
-    <t>Nobel ödülleri hangi ülkede verilmektedir?</t>
-  </si>
-  <si>
-    <t>Fransa</t>
-  </si>
-  <si>
-    <t>İngiltere</t>
-  </si>
-  <si>
-    <t>İsveç</t>
-  </si>
-  <si>
-    <t>Hollanda</t>
-  </si>
-  <si>
-    <t>Güneş sistemindeki en büyük gezegen hangisidir?</t>
-  </si>
-  <si>
-    <t>Uranüs</t>
-  </si>
-  <si>
-    <t>Jüpiter</t>
-  </si>
-  <si>
-    <t>Satürn</t>
-  </si>
-  <si>
-    <t>Merkür</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Asya'da yer alan ve "Dünya'nın çatısı" olarak bilinen yer neresidir?</t>
-  </si>
-  <si>
-    <t>Tibet</t>
-  </si>
-  <si>
-    <t>Pireneler</t>
-  </si>
-  <si>
-    <t>Petra</t>
-  </si>
-  <si>
-    <t>Kafkas</t>
-  </si>
-  <si>
-    <t>İnsan vücudundaki en büyük organ hangisidir?</t>
-  </si>
-  <si>
-    <t>Karaciğer</t>
-  </si>
-  <si>
-    <t>Beyin</t>
-  </si>
-  <si>
-    <t>Kalp</t>
-  </si>
-  <si>
-    <t>Akciğer</t>
-  </si>
-  <si>
-    <t>"Sefiller" romanının yazarı kimdir?</t>
-  </si>
-  <si>
-    <t>Franz Kafka</t>
-  </si>
-  <si>
-    <t>Victor Hugo</t>
-  </si>
-  <si>
-    <t>Dostoyevski</t>
-  </si>
-  <si>
-    <t>Nikolay Gogol</t>
-  </si>
-  <si>
-    <t>Işık yılı, neyi ölçmek için kullanılan bir birimdir?</t>
-  </si>
-  <si>
-    <t>Zaman</t>
-  </si>
-  <si>
-    <t>Hız</t>
-  </si>
-  <si>
-    <t>Mesafe</t>
-  </si>
-  <si>
-    <t>Kütle</t>
-  </si>
-  <si>
-    <t>"Rönesans'ın beşiği" olarak bilinen İtalyan şehri hangisidir?</t>
-  </si>
-  <si>
-    <t>Floransa</t>
-  </si>
-  <si>
-    <t>Milano</t>
-  </si>
-  <si>
-    <t>Roma</t>
-  </si>
-  <si>
-    <t>Napoli</t>
-  </si>
-  <si>
-    <t>Grönland hangi ülkeye bağlı özerk bir bölgedir?</t>
-  </si>
-  <si>
-    <t>Danimarka</t>
-  </si>
-  <si>
-    <t>Finlandiya</t>
-  </si>
-  <si>
-    <t>Norveç</t>
-  </si>
-  <si>
-    <t>Klasik müzikte, bir eseri yöneten kişiye ne ad verilir?</t>
-  </si>
-  <si>
-    <t>Besteci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solist </t>
-  </si>
-  <si>
-    <t>Orkestra</t>
-  </si>
-  <si>
-    <t>Şef</t>
-  </si>
-  <si>
-    <t>"Milli Spor" olarak kabul edilen ve olimpiyatlarda yer almayan spor hangisidir?</t>
-  </si>
-  <si>
-    <t>Güreş</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Atıcılık </t>
-  </si>
-  <si>
-    <t>Cirit</t>
-  </si>
-  <si>
-    <t>Halter</t>
+    <t>Hepsi</t>
+  </si>
+  <si>
+    <t>Hangisi bir BI toolu değildir?</t>
+  </si>
+  <si>
+    <t>SAP BI</t>
+  </si>
+  <si>
+    <t>Tableau</t>
+  </si>
+  <si>
+    <t>Qlick</t>
+  </si>
+  <si>
+    <t>Matlab</t>
+  </si>
+  <si>
+    <t>Dumbledore Hogwart ta her sınıfın yıllık malzeme harcamalarını takip etmek istiyor. SAP’de hangi tanım kullanılır?</t>
+  </si>
+  <si>
+    <t>House Bank</t>
+  </si>
+  <si>
+    <t>Cost Center</t>
+  </si>
+  <si>
+    <t>Internal Order</t>
+  </si>
+  <si>
+    <t>İstanbul ofis ile Gebze ofis arası kaç km?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BTIS’nin açılımı nedir? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilgi Teknolojileri İyileştirme Stratejileri </t>
+  </si>
+  <si>
+    <t>Bütün Ticket'lar İçin Sorumlu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilgi Teknolojileri İş Çözümleri </t>
+  </si>
+  <si>
+    <t>Bilgi Transferi ve İnteraktif Sistemler</t>
+  </si>
+  <si>
+    <t>SAP MII'nin bir süper gücü olsaydı ne olurdu?</t>
+  </si>
+  <si>
+    <t>Zamanda yolculuk</t>
+  </si>
+  <si>
+    <t>Fabrikada görünmezlik</t>
+  </si>
+  <si>
+    <t>Gerçek zamanlı veriyle tüm üretimi şeffaf hale getirme</t>
+  </si>
+  <si>
+    <t>Çalışanların yerine rapor yazma</t>
+  </si>
+  <si>
+    <t>SuccessFactors “Learning Management System (LMS)” modülü ne işe yarar?</t>
+  </si>
+  <si>
+    <t>E-posta yönetimi</t>
+  </si>
+  <si>
+    <t>Uzaktan eğitim ve çalışan gelişimi süreçlerini yönetmek</t>
+  </si>
+  <si>
+    <t>Stok takibi yapmak</t>
+  </si>
+  <si>
+    <t>Vardiya planı oluşturmak</t>
+  </si>
+  <si>
+    <t>Toplantıda herkes farklı şeyler söylüyorsa, iş analisti ne yapmalıdır?</t>
+  </si>
+  <si>
+    <t>Tartışmayı bitirip kahve molası vermek</t>
+  </si>
+  <si>
+    <t>Tüm görüşleri not alıp ortak noktayı bulmaya çalışmak</t>
+  </si>
+  <si>
+    <t>En yüksek sesli konuşanın dediğini kabul etmek</t>
+  </si>
+  <si>
+    <t>Toplantıyı sessizce terk etmek</t>
+  </si>
+  <si>
+    <t>Teklif oluştururken müşteri alanı boş bırakılırsa ne olur?</t>
+  </si>
+  <si>
+    <t>Sistem uyarı verir ve teklif kaydedilemez</t>
+  </si>
+  <si>
+    <t>Müşteri kendi kendine seçilir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sipariş havada kaybolur </t>
+  </si>
+  <si>
+    <t>SAP sistemden atar</t>
+  </si>
+  <si>
+    <t>BREAK-POINT ile DEBUG MODE arasındaki ilişki nedir?</t>
+  </si>
+  <si>
+    <t>BREAK-POINT debug modunu başlatır</t>
+  </si>
+  <si>
+    <t>Debug modu BREAK-POINT’i bulur</t>
+  </si>
+  <si>
+    <t>İkisi de geliştiricinin “yakala-kaç” oyunu gibidir</t>
+  </si>
+  <si>
+    <t>İş zekası modülü ile uğraşan birinin ne yapması beklenmez?</t>
+  </si>
+  <si>
+    <t>CO modülünün temel amacı nedir?</t>
+  </si>
+  <si>
+    <t>Ürün maliyetlerini ve iç raporlamayı yönetmek</t>
+  </si>
+  <si>
+    <t>Satış fiyatlarını belirlemek</t>
+  </si>
+  <si>
+    <t>Banka hesaplarını yönetmek</t>
+  </si>
+  <si>
+    <t>JIRA'da Bilgi teknolojilerine ait kaç adet proje bulunmaktadır?</t>
+  </si>
+  <si>
+    <t>SAP’de en çok korkulan ekran hangisidir?</t>
+  </si>
+  <si>
+    <t>SM37 – İş Listesi</t>
+  </si>
+  <si>
+    <t>ST22 – Dump Raporu</t>
+  </si>
+  <si>
+    <t>SU01 – Kullanıcı Oluşturma</t>
+  </si>
+  <si>
+    <t>SE80 – Object Navigator</t>
+  </si>
+  <si>
+    <t>SAP MII hangi iki sistem arasında köprü görevi görür?</t>
+  </si>
+  <si>
+    <t>ERP ve CRM</t>
+  </si>
+  <si>
+    <t>MES ve ERP</t>
+  </si>
+  <si>
+    <t>SCM ve SRM</t>
+  </si>
+  <si>
+    <t>HCM ve BI</t>
+  </si>
+  <si>
+    <t>SAP sistemine yanlış veri girerseniz ne olur?</t>
+  </si>
+  <si>
+    <t>Sistem kahve molası verir</t>
+  </si>
+  <si>
+    <t>Veri reddedilir veya hata alırsınız</t>
+  </si>
+  <si>
+    <t>Patron size alkış tutar</t>
+  </si>
+  <si>
+    <t>Bilgisayar patlar</t>
+  </si>
+  <si>
+    <t>Büyük işletmelerde kullanılan uygulamaların verileri yerel ya da cloud da nerede tutulur?</t>
+  </si>
+  <si>
+    <t>Dolaplarda</t>
+  </si>
+  <si>
+    <t>Dosyalarda</t>
+  </si>
+  <si>
+    <t>Buzdolabında</t>
+  </si>
+  <si>
+    <t>Veritabanında</t>
+  </si>
+  <si>
+    <t>Rpa ne demek ?</t>
+  </si>
+  <si>
+    <t>Robotic Programing Automation</t>
+  </si>
+  <si>
+    <t>Robotic Programing Authentication</t>
+  </si>
+  <si>
+    <t>Robotic Process Automation</t>
+  </si>
+  <si>
+    <t>Robotic Process Authentication</t>
+  </si>
+  <si>
+    <t>SAP’nin ERP açılımı aşağıdakilerden hangisi değildir?</t>
+  </si>
+  <si>
+    <t>Enterprise Resource Planning</t>
+  </si>
+  <si>
+    <t>Kurumsal Kaynak Planlama</t>
+  </si>
+  <si>
+    <t>Resource &amp; Enterprise Planning</t>
+  </si>
+  <si>
+    <t>En Rahat Patron</t>
+  </si>
+  <si>
+    <t>Kod hatalı çalıştığında</t>
+  </si>
+  <si>
+    <t>Koşul sağlandığında veya işlem başarılı olduğunda</t>
+  </si>
+  <si>
+    <t>Sistem saatini gösterdiğinde</t>
+  </si>
+  <si>
+    <t>Bellek boş olduğunda</t>
+  </si>
+  <si>
+    <t>SAP MM modülünde aşağıdakilerden hangisi bulunmaz?</t>
+  </si>
+  <si>
+    <t>Malzeme Yönetimi</t>
+  </si>
+  <si>
+    <t>Satınalma</t>
+  </si>
+  <si>
+    <t>Depo Yönetimi</t>
+  </si>
+  <si>
+    <t>Moda ve Makyaj Yönetimi</t>
+  </si>
+  <si>
+    <r>
+      <t>SY-SUBRC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="162"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> değeri ne zaman 0 olur?</t>
+    </r>
+  </si>
+  <si>
+    <t>Raporlarına hatalı dendiğinde doğru olduğunu ispatlamaya çalışmamalı</t>
+  </si>
+  <si>
+    <t>İnsanların arkasında oturup, "Excel böyle mi kullanılır? Şu formülü yaz." Diye maydanoz olmalı</t>
+  </si>
+  <si>
+    <t>Öyle istenen raporları yapmalı</t>
+  </si>
+  <si>
+    <t>Süreci başından alıp sonuna kadar götürmeli</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,6 +359,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="162"/>
     </font>
   </fonts>
   <fills count="2">
@@ -245,9 +394,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -581,19 +732,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83B9F140-7C0B-4521-B644-B522204F1902}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F608FC60-8EF4-4635-B0AF-614F7986C937}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="27.08984375" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" customWidth="1"/>
-    <col min="3" max="3" width="14.7265625" customWidth="1"/>
-    <col min="4" max="4" width="16.6328125" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" customWidth="1"/>
-    <col min="6" max="6" width="17.36328125" customWidth="1"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="19.36328125" customWidth="1"/>
+    <col min="3" max="3" width="16.6328125" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="21.7265625" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -601,219 +752,603 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
+      <c r="B4">
+        <v>30</v>
+      </c>
+      <c r="C4">
+        <v>32</v>
+      </c>
+      <c r="D4">
+        <v>34</v>
+      </c>
+      <c r="E4">
+        <v>36</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>25</v>
       </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="E6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
+      <c r="F6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C7" t="s">
         <v>29</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D7" t="s">
         <v>30</v>
       </c>
-      <c r="F6">
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B8" t="s">
         <v>33</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D8" t="s">
         <v>35</v>
       </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="E8" t="s">
         <v>36</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
         <v>37</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B9" t="s">
         <v>38</v>
       </c>
-      <c r="D8" t="s">
+      <c r="C9" t="s">
         <v>39</v>
       </c>
-      <c r="E8" t="s">
+      <c r="D9" t="s">
         <v>40</v>
       </c>
-      <c r="F8">
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>42</v>
       </c>
-      <c r="D9" t="s">
+      <c r="B10" t="s">
         <v>43</v>
       </c>
-      <c r="E9" t="s">
+      <c r="C10" t="s">
         <v>44</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="D10" t="s">
         <v>45</v>
       </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
-      </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
         <v>50</v>
       </c>
-      <c r="B11" t="s">
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
         <v>51</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
         <v>52</v>
       </c>
-      <c r="D11" t="s">
+      <c r="B14" t="s">
         <v>53</v>
       </c>
-      <c r="E11" t="s">
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" t="s">
         <v>54</v>
       </c>
-      <c r="F11">
+      <c r="E14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14">
         <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Belge" ma:contentTypeID="0x010100F3A0D95866192D4A8FE078725DE18D29" ma:contentTypeVersion="1" ma:contentTypeDescription="Yeni belge oluşturun." ma:contentTypeScope="" ma:versionID="80e96d3dd7133ebaeb7136ae549c143d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f5b383e4-2c14-4d59-b524-abe0725e3c80" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58430cb18919005ecb61a66e8e4d9f" ns3:_="">
+    <xsd:import namespace="f5b383e4-2c14-4d59-b524-abe0725e3c80"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f5b383e4-2c14-4d59-b524-abe0725e3c80" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="İçerik Türü"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Başlık"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B01C06F-6D00-493B-B35C-9065C7127AFE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f5b383e4-2c14-4d59-b524-abe0725e3c80"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B45F473-7EC0-4C9B-BCC0-940837FA973F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="f5b383e4-2c14-4d59-b524-abe0725e3c80"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EBD7F53-4567-4317-BBB6-2312B9448A74}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/questions.xlsx
+++ b/questions.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bt.stajyer\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E27070-2BBA-408E-9F38-69CE9BE42433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B05765D8-1BFC-41D6-B916-63AAD90E4244}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="111">
   <si>
     <t>question</t>
   </si>
@@ -338,11 +332,56 @@
   <si>
     <t>Süreci başından alıp sonuna kadar götürmeli</t>
   </si>
+  <si>
+    <t>BT ekibinde "efsane replik" hangisidir?</t>
+  </si>
+  <si>
+    <t>Teknokta açar mısın?</t>
+  </si>
+  <si>
+    <t>Bende çalışıyor?</t>
+  </si>
+  <si>
+    <t>Kullanıcı hatası olabillir mi?</t>
+  </si>
+  <si>
+    <t>İstesek 1 saatte çözeriz</t>
+  </si>
+  <si>
+    <t>Yöneticinizin en çok kullandığı cümle hangisidir?</t>
+  </si>
+  <si>
+    <t>Bunu yarına yetiştirir misiniz?</t>
+  </si>
+  <si>
+    <t>Aramızda kalsın</t>
+  </si>
+  <si>
+    <t>Toplantı kısa olacak, söz</t>
+  </si>
+  <si>
+    <t>Siz en iyisini bilirsiniz</t>
+  </si>
+  <si>
+    <t>Proje sonrası beklentileriniz ne olur?</t>
+  </si>
+  <si>
+    <t>Kahvaltı</t>
+  </si>
+  <si>
+    <t>Şirket dışı etkinlik</t>
+  </si>
+  <si>
+    <t>Motivasyonumuz tam, gerek yok 😊</t>
+  </si>
+  <si>
+    <t>Yeni proje haberini almak</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -725,23 +764,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F608FC60-8EF4-4635-B0AF-614F7986C937}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" customWidth="1"/>
-    <col min="3" max="3" width="16.6328125" customWidth="1"/>
-    <col min="4" max="4" width="21.453125" customWidth="1"/>
-    <col min="5" max="5" width="21.7265625" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.3984375" customWidth="1"/>
+    <col min="3" max="3" width="16.59765625" customWidth="1"/>
+    <col min="4" max="4" width="21.5" customWidth="1"/>
+    <col min="5" max="5" width="21.69921875" customWidth="1"/>
+    <col min="6" max="6" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -786,119 +825,119 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4">
-        <v>30</v>
-      </c>
-      <c r="C4">
-        <v>32</v>
-      </c>
-      <c r="D4">
-        <v>34</v>
-      </c>
-      <c r="E4">
-        <v>36</v>
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>32</v>
+      </c>
+      <c r="D5">
+        <v>34</v>
+      </c>
+      <c r="E5">
+        <v>36</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E6" t="s">
         <v>21</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>27</v>
+      <c r="A7" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -906,239 +945,239 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>92</v>
+        <v>6</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>5</v>
-      </c>
-      <c r="E13">
-        <v>6</v>
+        <v>46</v>
+      </c>
+      <c r="B13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" t="s">
+        <v>92</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" t="s">
-        <v>61</v>
+        <v>51</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="3" t="s">
-        <v>91</v>
+      <c r="A19" t="s">
+        <v>72</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="E20" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="F20">
         <v>3</v>
@@ -1146,21 +1185,81 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15">
+      <c r="A22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
         <v>77</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B24" t="s">
         <v>78</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C24" t="s">
         <v>79</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D24" t="s">
         <v>80</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E24" t="s">
         <v>81</v>
       </c>
-      <c r="F21">
+      <c r="F24">
         <v>3</v>
       </c>
     </row>
@@ -1171,6 +1270,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Belge" ma:contentTypeID="0x010100F3A0D95866192D4A8FE078725DE18D29" ma:contentTypeVersion="1" ma:contentTypeDescription="Yeni belge oluşturun." ma:contentTypeScope="" ma:versionID="80e96d3dd7133ebaeb7136ae549c143d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f5b383e4-2c14-4d59-b524-abe0725e3c80" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58430cb18919005ecb61a66e8e4d9f" ns3:_="">
     <xsd:import namespace="f5b383e4-2c14-4d59-b524-abe0725e3c80"/>
@@ -1296,35 +1410,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B01C06F-6D00-493B-B35C-9065C7127AFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EBD7F53-4567-4317-BBB6-2312B9448A74}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f5b383e4-2c14-4d59-b524-abe0725e3c80"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1346,9 +1435,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EBD7F53-4567-4317-BBB6-2312B9448A74}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B01C06F-6D00-493B-B35C-9065C7127AFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f5b383e4-2c14-4d59-b524-abe0725e3c80"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>